--- a/ML-Entrees/ig/StructureDefinition-fr-lm-evolution-adverse-event.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-evolution-adverse-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -261,16 +261,6 @@
   </si>
   <si>
     <t>Code de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-evolution-adverse-event.statut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l'entrée</t>
   </si>
   <si>
     <t>fr-lm-evolution-adverse-event.evolution</t>
@@ -578,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.203125" customWidth="true" bestFit="true"/>
@@ -956,13 +946,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1025,106 +1015,6 @@
         <v>73</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-evolution-adverse-event.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-evolution-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-evolution-adverse-event.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-evolution-adverse-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
